--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="June 2025" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>NEW</x:t>
@@ -100,7 +64,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -127,12 +91,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -143,17 +101,23 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -161,20 +125,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -202,15 +159,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="15">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -222,14 +179,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -247,10 +204,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -261,13 +218,30 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -422,37 +396,37 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -461,16 +435,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -479,67 +450,78 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -551,20 +533,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -572,6 +554,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -835,188 +821,184 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+      <x:c r="H6" s="13">
         <x:v>45825.2509606481</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45825.2509837963</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>2744256</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45825.8750462963</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="B9" s="17" t="s">
+        <x:v>7</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>8</x:v>
       </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>21</x:v>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>22</x:v>
+      <x:c r="B12" s="26" t="s">
+        <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -22,9 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RONALD MANINANG</x:t>
   </x:si>
   <x:si>
     <x:t>NEW</x:t>
@@ -125,7 +128,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -159,7 +162,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -204,10 +207,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -218,30 +221,13 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -423,10 +409,13 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -435,13 +424,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -450,11 +439,8 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -490,38 +476,46 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -533,11 +527,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -545,8 +535,12 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -554,10 +548,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -806,7 +796,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -823,7 +815,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45809</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -884,22 +876,22 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45825.2509606481</x:v>
@@ -917,7 +909,7 @@
         <x:v>45825.8750462963</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -938,29 +930,27 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -969,41 +959,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>1</x:v>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>10</x:v>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -1984,13 +1982,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -846,7 +846,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -914,7 +914,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -22,12 +22,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>RONALD MANINANG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>NEW</x:t>
@@ -67,7 +103,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -112,15 +148,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -135,6 +171,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -382,27 +425,24 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -424,10 +464,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -440,7 +483,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -471,36 +514,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -527,15 +554,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -848,18 +875,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -877,73 +892,85 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45825.2509606481</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45825.2509837963</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>2744256</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45825.8750462963</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -961,44 +988,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>10</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>RONALD MANINANG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -103,7 +106,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -143,6 +146,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -414,14 +441,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -434,56 +470,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -514,67 +550,79 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -803,58 +851,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -897,79 +945,79 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45825.2509606481</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45825.2509837963</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>2744256</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45825.8750462963</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -988,44 +1036,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2012,7 +2060,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>NEW</x:t>
@@ -103,10 +139,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -151,15 +189,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -175,15 +205,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -198,13 +228,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -441,26 +464,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -470,56 +493,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -550,79 +576,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -851,78 +889,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -943,7 +993,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -983,102 +1033,139 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45825.2509606481</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>45825.2509837963</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>2744256</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>45825.8750462963</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>23</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2057,14 +2144,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>NEW</x:t>
@@ -144,7 +108,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -188,14 +152,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -210,10 +166,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -228,6 +192,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -472,16 +443,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -493,24 +464,21 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -529,10 +497,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -545,7 +516,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -576,28 +547,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -612,10 +575,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -640,15 +599,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -993,7 +952,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1033,139 +992,102 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45825.2509606481</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45825.2509837963</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>2744256</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45825.8750462963</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2149,10 +2071,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -82,6 +82,9 @@
   </x:si>
   <x:si>
     <x:t>61-6-2025-1006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2744256</x:t>
   </x:si>
   <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
@@ -1011,22 +1014,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>45825.2509606481</x:v>
+        <x:v>45825.2509637269</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>2744256</x:v>
+        <x:v>45825.2509878357</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>4530</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>45825.8750462963</x:v>
+        <x:v>45825.8750542361</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1046,7 +1049,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s"/>
       <x:c r="D11" s="18" t="s"/>
@@ -1055,13 +1058,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="20" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s"/>
       <x:c r="D12" s="21" t="s"/>
       <x:c r="E12" s="21" t="s"/>
       <x:c r="F12" s="22" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
@@ -1077,7 +1080,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="26" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s"/>
       <x:c r="D14" s="27" t="s"/>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -955,7 +955,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -995,7 +995,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>RONALD MANINANG</x:t>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>RONALD MANINANG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -438,7 +435,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -455,6 +452,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -519,7 +519,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -555,6 +555,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -921,20 +925,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45809</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -957,79 +961,79 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>45825.2509637269</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45825.2509878357</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45825.2509637269</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45825.2509878357</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="K8" s="17" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>45825.8750542361</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45825.8750542361</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1048,44 +1052,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
+++ b/reports/service-tracking-report-RONALD-MANINANG-evaluator-cache-serviceTracking-RONALD-MANINANG-III-202501-202612.xlsx
@@ -108,7 +108,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -148,14 +148,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -435,7 +427,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -446,16 +438,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -467,59 +456,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -554,79 +543,75 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -928,17 +913,17 @@
       <x:c r="B5" s="12">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -961,78 +946,78 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>45825.2509637269</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>45825.2509878357</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>45825.8750542361</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -1052,44 +1037,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
